--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129914678</v>
       </c>
       <c r="B2" t="n">
-        <v>100975</v>
+        <v>100979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129914809</v>
       </c>
       <c r="B3" t="n">
-        <v>97659</v>
+        <v>97663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129914678</v>
       </c>
       <c r="B2" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129914809</v>
       </c>
       <c r="B3" t="n">
-        <v>97663</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129914678</v>
       </c>
       <c r="B2" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129914809</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>97706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129914678</v>
       </c>
       <c r="B2" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129914809</v>
       </c>
       <c r="B3" t="n">
-        <v>97706</v>
+        <v>97793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129914678</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>101022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129914809</v>
       </c>
       <c r="B3" t="n">
-        <v>97793</v>
+        <v>97706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129914678</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>101325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129914809</v>
+        <v>129914732</v>
       </c>
       <c r="B3" t="n">
-        <v>97793</v>
+        <v>101325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,22 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485970</v>
+        <v>486053</v>
       </c>
       <c r="R3" t="n">
-        <v>6994059</v>
+        <v>6994074</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,7 +850,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Lockne</t>
+          <t>Marieby</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -856,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +894,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129914809</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vålbackån, Vålbackån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485970</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6994059</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58931-2025 artfynd.xlsx
+++ b/artfynd/A 58931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914732</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>